--- a/terminology/CodeSystem-dlp-atc.xlsx
+++ b/terminology/CodeSystem-dlp-atc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T18:33:07+01:00</t>
+    <t>2026-02-02T08:04:31+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
